--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -1695,10 +1695,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128526246</v>
+        <v>128521099</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>91448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,34 +1706,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västbodarna, Västbodarna, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488615</v>
+        <v>488553</v>
       </c>
       <c r="R10" t="n">
-        <v>7061764</v>
+        <v>7061525</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1779,7 +1784,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1794,12 +1799,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1817,7 +1822,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128524649</v>
+        <v>128526246</v>
       </c>
       <c r="B11" t="n">
         <v>79083</v>
@@ -1848,17 +1853,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Västbodarna, Västbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488534</v>
+        <v>488615</v>
       </c>
       <c r="R11" t="n">
-        <v>7061682</v>
+        <v>7061764</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1885,19 +1890,9 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1949,10 +1944,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128521099</v>
+        <v>128524649</v>
       </c>
       <c r="B12" t="n">
-        <v>91448</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,42 +1955,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488553</v>
+        <v>488534</v>
       </c>
       <c r="R12" t="n">
-        <v>7061525</v>
+        <v>7061682</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2022,11 +2012,21 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2579,7 +2579,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128526042</v>
+        <v>128529478</v>
       </c>
       <c r="B17" t="n">
         <v>57685</v>
@@ -2608,24 +2608,27 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488537</v>
+        <v>488440</v>
       </c>
       <c r="R17" t="n">
-        <v>7061782</v>
+        <v>7061748</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2655,6 +2658,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2706,7 +2714,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128529478</v>
+        <v>128526042</v>
       </c>
       <c r="B18" t="n">
         <v>57685</v>
@@ -2735,27 +2743,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488440</v>
+        <v>488537</v>
       </c>
       <c r="R18" t="n">
-        <v>7061748</v>
+        <v>7061782</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2785,11 +2790,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3730,7 +3730,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128520722</v>
+        <v>128524030</v>
       </c>
       <c r="B26" t="n">
         <v>57685</v>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488547</v>
+        <v>488370</v>
       </c>
       <c r="R26" t="n">
-        <v>7061612</v>
+        <v>7061528</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3867,7 +3867,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128524030</v>
+        <v>128520722</v>
       </c>
       <c r="B27" t="n">
         <v>57685</v>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488370</v>
+        <v>488547</v>
       </c>
       <c r="R27" t="n">
-        <v>7061528</v>
+        <v>7061612</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -1695,10 +1695,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128521099</v>
+        <v>128526246</v>
       </c>
       <c r="B10" t="n">
-        <v>91448</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,39 +1706,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Västbodarna, Västbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488553</v>
+        <v>488615</v>
       </c>
       <c r="R10" t="n">
-        <v>7061525</v>
+        <v>7061764</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1784,7 +1779,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1799,12 +1794,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1822,7 +1817,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128526246</v>
+        <v>128524649</v>
       </c>
       <c r="B11" t="n">
         <v>79083</v>
@@ -1853,17 +1848,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västbodarna, Västbodarna, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488615</v>
+        <v>488534</v>
       </c>
       <c r="R11" t="n">
-        <v>7061764</v>
+        <v>7061682</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1890,9 +1885,19 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1944,10 +1949,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128524649</v>
+        <v>128521099</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>91448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,37 +1960,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488534</v>
+        <v>488553</v>
       </c>
       <c r="R12" t="n">
-        <v>7061682</v>
+        <v>7061525</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2012,21 +2022,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -3466,38 +3466,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128522759</v>
+        <v>128525531</v>
       </c>
       <c r="B24" t="n">
-        <v>98488</v>
+        <v>57685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488182</v>
+        <v>488486</v>
       </c>
       <c r="R24" t="n">
-        <v>7061439</v>
+        <v>7061727</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3544,14 +3544,24 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Vid en liten bäck.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3566,6 +3576,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3583,7 +3613,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128525531</v>
+        <v>128524030</v>
       </c>
       <c r="B25" t="n">
         <v>57685</v>
@@ -3628,13 +3658,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488486</v>
+        <v>488370</v>
       </c>
       <c r="R25" t="n">
-        <v>7061727</v>
+        <v>7061528</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3661,24 +3691,14 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3692,7 +3712,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3730,7 +3750,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128524030</v>
+        <v>128520722</v>
       </c>
       <c r="B26" t="n">
         <v>57685</v>
@@ -3775,10 +3795,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488370</v>
+        <v>488547</v>
       </c>
       <c r="R26" t="n">
-        <v>7061528</v>
+        <v>7061612</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3815,7 +3835,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3829,7 +3849,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3867,38 +3887,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128520722</v>
+        <v>128522759</v>
       </c>
       <c r="B27" t="n">
-        <v>57685</v>
+        <v>98488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3912,13 +3932,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488547</v>
+        <v>488182</v>
       </c>
       <c r="R27" t="n">
-        <v>7061612</v>
+        <v>7061439</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3952,7 +3972,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
+          <t>Vid en liten bäck.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3967,26 +3987,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128523976</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>128520460</v>
       </c>
       <c r="B3" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>128520214</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>128524370</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>128520624</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>128526060</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128524385</v>
       </c>
       <c r="B8" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>128526315</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128526246</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>128524649</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>128521099</v>
       </c>
       <c r="B12" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>128522990</v>
       </c>
       <c r="B13" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>128520994</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128520836</v>
       </c>
       <c r="B15" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>128524584</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128529478</v>
       </c>
       <c r="B17" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>128526042</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128519986</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>128526001</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>128525407</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>128520317</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>128524203</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128525531</v>
       </c>
       <c r="B24" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128524030</v>
+        <v>128520722</v>
       </c>
       <c r="B25" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488370</v>
+        <v>488547</v>
       </c>
       <c r="R25" t="n">
-        <v>7061528</v>
+        <v>7061612</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3750,10 +3750,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128520722</v>
+        <v>128524030</v>
       </c>
       <c r="B26" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488547</v>
+        <v>488370</v>
       </c>
       <c r="R26" t="n">
-        <v>7061612</v>
+        <v>7061528</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3890,7 +3890,7 @@
         <v>128522759</v>
       </c>
       <c r="B27" t="n">
-        <v>98488</v>
+        <v>98496</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128523237</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>128525134</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>128521676</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>128520359</v>
       </c>
       <c r="B31" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>128539542</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>128521198</v>
       </c>
       <c r="B33" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>128522630</v>
       </c>
       <c r="B34" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>128529638</v>
       </c>
       <c r="B35" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>128529626</v>
       </c>
       <c r="B36" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>128523788</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>128525266</v>
       </c>
       <c r="B38" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128523640</v>
       </c>
       <c r="B39" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>128524326</v>
       </c>
       <c r="B40" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>128539465</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>128529649</v>
       </c>
       <c r="B42" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128520460</v>
       </c>
       <c r="B3" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128524370</v>
+        <v>128520624</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,37 +1091,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488532</v>
+        <v>488560</v>
       </c>
       <c r="R5" t="n">
-        <v>7061632</v>
+        <v>7061623</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1153,6 +1158,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gammal gran  som står nära en grov asp.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1161,6 +1171,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1177,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128520624</v>
+        <v>128524370</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,42 +1223,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488560</v>
+        <v>488532</v>
       </c>
       <c r="R6" t="n">
-        <v>7061623</v>
+        <v>7061632</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,11 +1285,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gammal gran  som står nära en grov asp.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1268,31 +1293,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1449,7 +1449,7 @@
         <v>128524385</v>
       </c>
       <c r="B8" t="n">
-        <v>91454</v>
+        <v>91460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>128521099</v>
       </c>
       <c r="B12" t="n">
-        <v>91454</v>
+        <v>91460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>128522990</v>
       </c>
       <c r="B13" t="n">
-        <v>97460</v>
+        <v>97466</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3750,38 +3750,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128524030</v>
+        <v>128522759</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>98502</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3795,13 +3795,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488370</v>
+        <v>488182</v>
       </c>
       <c r="R26" t="n">
-        <v>7061528</v>
+        <v>7061439</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Vid en liten bäck.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3849,27 +3849,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3887,38 +3867,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128522759</v>
+        <v>128524030</v>
       </c>
       <c r="B27" t="n">
-        <v>98496</v>
+        <v>57689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3932,13 +3912,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488182</v>
+        <v>488370</v>
       </c>
       <c r="R27" t="n">
-        <v>7061439</v>
+        <v>7061528</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3972,7 +3952,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Vid en liten bäck.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3986,7 +3966,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4651,7 +4651,7 @@
         <v>128521198</v>
       </c>
       <c r="B33" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>128522630</v>
       </c>
       <c r="B34" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128523640</v>
       </c>
       <c r="B39" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>128524326</v>
       </c>
       <c r="B40" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -3613,7 +3613,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128520722</v>
+        <v>128524030</v>
       </c>
       <c r="B25" t="n">
         <v>57689</v>
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488547</v>
+        <v>488370</v>
       </c>
       <c r="R25" t="n">
-        <v>7061612</v>
+        <v>7061528</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3750,38 +3750,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128522759</v>
+        <v>128520722</v>
       </c>
       <c r="B26" t="n">
-        <v>98502</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3795,13 +3795,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488182</v>
+        <v>488547</v>
       </c>
       <c r="R26" t="n">
-        <v>7061439</v>
+        <v>7061612</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Vid en liten bäck.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3850,6 +3850,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3867,38 +3887,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128524030</v>
+        <v>128522759</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>98502</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3912,13 +3932,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488370</v>
+        <v>488182</v>
       </c>
       <c r="R27" t="n">
-        <v>7061528</v>
+        <v>7061439</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3952,7 +3972,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Vid en liten bäck.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3966,27 +3986,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128520460</v>
       </c>
       <c r="B3" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>128520214</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128520624</v>
+        <v>128524370</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,42 +1091,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488560</v>
+        <v>488532</v>
       </c>
       <c r="R5" t="n">
-        <v>7061623</v>
+        <v>7061632</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1158,11 +1153,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gammal gran  som står nära en grov asp.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1171,31 +1161,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1212,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128524370</v>
+        <v>128520624</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,37 +1188,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488532</v>
+        <v>488560</v>
       </c>
       <c r="R6" t="n">
-        <v>7061632</v>
+        <v>7061623</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1285,6 +1255,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gammal gran  som står nära en grov asp.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1293,6 +1268,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1449,7 +1449,7 @@
         <v>128524385</v>
       </c>
       <c r="B8" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128526315</v>
+        <v>128521099</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>91462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,37 +1584,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västbodarna, Västbodarna, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488619</v>
+        <v>488553</v>
       </c>
       <c r="R9" t="n">
-        <v>7061800</v>
+        <v>7061525</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1672,12 +1677,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1695,10 +1700,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128526246</v>
+        <v>128526315</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,13 +1735,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488615</v>
+        <v>488619</v>
       </c>
       <c r="R10" t="n">
-        <v>7061764</v>
+        <v>7061800</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1817,10 +1822,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128524649</v>
+        <v>128526246</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,17 +1853,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Västbodarna, Västbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488534</v>
+        <v>488615</v>
       </c>
       <c r="R11" t="n">
-        <v>7061682</v>
+        <v>7061764</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1885,19 +1890,9 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1949,10 +1944,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128521099</v>
+        <v>128524649</v>
       </c>
       <c r="B12" t="n">
-        <v>91460</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,42 +1955,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488553</v>
+        <v>488534</v>
       </c>
       <c r="R12" t="n">
-        <v>7061525</v>
+        <v>7061682</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2022,11 +2012,21 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
         <v>128522990</v>
       </c>
       <c r="B13" t="n">
-        <v>97466</v>
+        <v>97468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2457,10 +2457,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128524584</v>
+        <v>128529478</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,37 +2468,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488499</v>
+        <v>488440</v>
       </c>
       <c r="R16" t="n">
-        <v>7061671</v>
+        <v>7061748</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2530,6 +2538,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2556,12 +2569,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2579,7 +2592,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128529478</v>
+        <v>128526042</v>
       </c>
       <c r="B17" t="n">
         <v>57689</v>
@@ -2608,27 +2621,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488440</v>
+        <v>488537</v>
       </c>
       <c r="R17" t="n">
-        <v>7061748</v>
+        <v>7061782</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2658,11 +2668,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2714,10 +2719,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128526042</v>
+        <v>128524584</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2725,42 +2730,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488537</v>
+        <v>488499</v>
       </c>
       <c r="R18" t="n">
-        <v>7061782</v>
+        <v>7061671</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2844,7 +2844,7 @@
         <v>128519986</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>128526001</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>128525407</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>128520317</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>128524203</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>128522759</v>
       </c>
       <c r="B27" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128523237</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>128525134</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>128521676</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>128539542</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>128521198</v>
       </c>
       <c r="B33" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>128522630</v>
       </c>
       <c r="B34" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>128529626</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>128523788</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128523640</v>
       </c>
       <c r="B39" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>128524326</v>
       </c>
       <c r="B40" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>128539465</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -1573,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128521099</v>
+        <v>128526315</v>
       </c>
       <c r="B9" t="n">
-        <v>91462</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,42 +1584,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Västbodarna, Västbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488553</v>
+        <v>488619</v>
       </c>
       <c r="R9" t="n">
-        <v>7061525</v>
+        <v>7061800</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1662,7 +1657,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1677,12 +1672,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1700,7 +1695,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128526315</v>
+        <v>128526246</v>
       </c>
       <c r="B10" t="n">
         <v>79089</v>
@@ -1735,13 +1730,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488619</v>
+        <v>488615</v>
       </c>
       <c r="R10" t="n">
-        <v>7061800</v>
+        <v>7061764</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1822,7 +1817,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128526246</v>
+        <v>128524649</v>
       </c>
       <c r="B11" t="n">
         <v>79089</v>
@@ -1853,17 +1848,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västbodarna, Västbodarna, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488615</v>
+        <v>488534</v>
       </c>
       <c r="R11" t="n">
-        <v>7061764</v>
+        <v>7061682</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1890,9 +1885,19 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1944,10 +1949,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128524649</v>
+        <v>128521099</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>91462</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,37 +1960,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488534</v>
+        <v>488553</v>
       </c>
       <c r="R12" t="n">
-        <v>7061682</v>
+        <v>7061525</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2012,21 +2022,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -3890,7 +3890,7 @@
         <v>128522759</v>
       </c>
       <c r="B27" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>128521198</v>
       </c>
       <c r="B33" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>128522630</v>
       </c>
       <c r="B34" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128523640</v>
       </c>
       <c r="B39" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>128524326</v>
       </c>
       <c r="B40" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -1573,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128526315</v>
+        <v>128521099</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>91462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,37 +1584,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västbodarna, Västbodarna, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488619</v>
+        <v>488553</v>
       </c>
       <c r="R9" t="n">
-        <v>7061800</v>
+        <v>7061525</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1672,12 +1677,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1695,7 +1700,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128526246</v>
+        <v>128526315</v>
       </c>
       <c r="B10" t="n">
         <v>79089</v>
@@ -1730,13 +1735,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488615</v>
+        <v>488619</v>
       </c>
       <c r="R10" t="n">
-        <v>7061764</v>
+        <v>7061800</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1817,7 +1822,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128524649</v>
+        <v>128526246</v>
       </c>
       <c r="B11" t="n">
         <v>79089</v>
@@ -1848,17 +1853,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Västbodarna, Västbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488534</v>
+        <v>488615</v>
       </c>
       <c r="R11" t="n">
-        <v>7061682</v>
+        <v>7061764</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1885,19 +1890,9 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1949,10 +1944,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128521099</v>
+        <v>128524649</v>
       </c>
       <c r="B12" t="n">
-        <v>91462</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,42 +1955,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488553</v>
+        <v>488534</v>
       </c>
       <c r="R12" t="n">
-        <v>7061525</v>
+        <v>7061682</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2022,11 +2012,21 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2457,10 +2457,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128529478</v>
+        <v>128524584</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,45 +2468,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488440</v>
+        <v>488499</v>
       </c>
       <c r="R16" t="n">
-        <v>7061748</v>
+        <v>7061671</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2538,11 +2530,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2569,12 +2556,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2592,7 +2579,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128526042</v>
+        <v>128529478</v>
       </c>
       <c r="B17" t="n">
         <v>57689</v>
@@ -2621,24 +2608,27 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488537</v>
+        <v>488440</v>
       </c>
       <c r="R17" t="n">
-        <v>7061782</v>
+        <v>7061748</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2668,6 +2658,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2719,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128524584</v>
+        <v>128526042</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,37 +2725,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488499</v>
+        <v>488537</v>
       </c>
       <c r="R18" t="n">
-        <v>7061671</v>
+        <v>7061782</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128520460</v>
       </c>
       <c r="B3" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128524385</v>
       </c>
       <c r="B8" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128521099</v>
+        <v>128526315</v>
       </c>
       <c r="B9" t="n">
-        <v>91462</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,42 +1584,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Västbodarna, Västbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488553</v>
+        <v>488619</v>
       </c>
       <c r="R9" t="n">
-        <v>7061525</v>
+        <v>7061800</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1662,7 +1657,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1677,12 +1672,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1700,7 +1695,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128526315</v>
+        <v>128526246</v>
       </c>
       <c r="B10" t="n">
         <v>79089</v>
@@ -1735,13 +1730,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488619</v>
+        <v>488615</v>
       </c>
       <c r="R10" t="n">
-        <v>7061800</v>
+        <v>7061764</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1822,7 +1817,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128526246</v>
+        <v>128524649</v>
       </c>
       <c r="B11" t="n">
         <v>79089</v>
@@ -1853,17 +1848,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västbodarna, Västbodarna, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488615</v>
+        <v>488534</v>
       </c>
       <c r="R11" t="n">
-        <v>7061764</v>
+        <v>7061682</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1890,9 +1885,19 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1944,10 +1949,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128524649</v>
+        <v>128521099</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>91463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,37 +1960,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488534</v>
+        <v>488553</v>
       </c>
       <c r="R12" t="n">
-        <v>7061682</v>
+        <v>7061525</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2012,21 +2022,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
         <v>128522990</v>
       </c>
       <c r="B13" t="n">
-        <v>97468</v>
+        <v>97469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128529478</v>
+        <v>128526042</v>
       </c>
       <c r="B17" t="n">
         <v>57689</v>
@@ -2608,27 +2608,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488440</v>
+        <v>488537</v>
       </c>
       <c r="R17" t="n">
-        <v>7061748</v>
+        <v>7061782</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2658,11 +2655,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2714,7 +2706,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128526042</v>
+        <v>128529478</v>
       </c>
       <c r="B18" t="n">
         <v>57689</v>
@@ -2743,24 +2735,27 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488537</v>
+        <v>488440</v>
       </c>
       <c r="R18" t="n">
-        <v>7061782</v>
+        <v>7061748</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2790,6 +2785,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3466,38 +3466,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128525531</v>
+        <v>128522759</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>98509</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488486</v>
+        <v>488182</v>
       </c>
       <c r="R24" t="n">
-        <v>7061727</v>
+        <v>7061439</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3544,24 +3544,14 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Vid en liten bäck.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3576,26 +3566,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3613,7 +3583,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128524030</v>
+        <v>128525531</v>
       </c>
       <c r="B25" t="n">
         <v>57689</v>
@@ -3658,13 +3628,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488370</v>
+        <v>488486</v>
       </c>
       <c r="R25" t="n">
-        <v>7061528</v>
+        <v>7061727</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3691,14 +3661,24 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3712,7 +3692,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3887,38 +3867,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128522759</v>
+        <v>128524030</v>
       </c>
       <c r="B27" t="n">
-        <v>98508</v>
+        <v>57689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3932,13 +3912,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488182</v>
+        <v>488370</v>
       </c>
       <c r="R27" t="n">
-        <v>7061439</v>
+        <v>7061528</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3972,7 +3952,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Vid en liten bäck.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3986,7 +3966,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4651,7 +4651,7 @@
         <v>128521198</v>
       </c>
       <c r="B33" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>128522630</v>
       </c>
       <c r="B34" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128523640</v>
       </c>
       <c r="B39" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>128524326</v>
       </c>
       <c r="B40" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128523976</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>128520460</v>
       </c>
       <c r="B3" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>128520214</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>128524370</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>128520624</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>128526060</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128524385</v>
       </c>
       <c r="B8" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128526315</v>
+        <v>128521099</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>91490</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,37 +1584,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västbodarna, Västbodarna, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488619</v>
+        <v>488553</v>
       </c>
       <c r="R9" t="n">
-        <v>7061800</v>
+        <v>7061525</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1672,12 +1677,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1695,10 +1700,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128526246</v>
+        <v>128526315</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,13 +1735,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488615</v>
+        <v>488619</v>
       </c>
       <c r="R10" t="n">
-        <v>7061764</v>
+        <v>7061800</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1817,10 +1822,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128524649</v>
+        <v>128526246</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,17 +1853,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Västbodarna, Västbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488534</v>
+        <v>488615</v>
       </c>
       <c r="R11" t="n">
-        <v>7061682</v>
+        <v>7061764</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1885,19 +1890,9 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1949,10 +1944,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128521099</v>
+        <v>128524649</v>
       </c>
       <c r="B12" t="n">
-        <v>91463</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,42 +1955,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488553</v>
+        <v>488534</v>
       </c>
       <c r="R12" t="n">
-        <v>7061525</v>
+        <v>7061682</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2022,11 +2012,21 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
         <v>128522990</v>
       </c>
       <c r="B13" t="n">
-        <v>97469</v>
+        <v>97496</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>128520994</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128520836</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2457,10 +2457,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128524584</v>
+        <v>128526042</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,37 +2468,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488499</v>
+        <v>488537</v>
       </c>
       <c r="R16" t="n">
-        <v>7061671</v>
+        <v>7061782</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2556,12 +2561,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2579,10 +2584,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128526042</v>
+        <v>128529478</v>
       </c>
       <c r="B17" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,24 +2613,27 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488537</v>
+        <v>488440</v>
       </c>
       <c r="R17" t="n">
-        <v>7061782</v>
+        <v>7061748</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2655,6 +2663,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2706,10 +2719,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128529478</v>
+        <v>128524584</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2717,45 +2730,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488440</v>
+        <v>488499</v>
       </c>
       <c r="R18" t="n">
-        <v>7061748</v>
+        <v>7061671</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2787,11 +2792,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2844,7 +2844,7 @@
         <v>128519986</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>128526001</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>128525407</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>128520317</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>128524203</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3466,38 +3466,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128522759</v>
+        <v>128525531</v>
       </c>
       <c r="B24" t="n">
-        <v>98509</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488182</v>
+        <v>488486</v>
       </c>
       <c r="R24" t="n">
-        <v>7061439</v>
+        <v>7061727</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3544,14 +3544,24 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Vid en liten bäck.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3566,6 +3576,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3583,10 +3613,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128525531</v>
+        <v>128520722</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3628,13 +3658,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488486</v>
+        <v>488547</v>
       </c>
       <c r="R25" t="n">
-        <v>7061727</v>
+        <v>7061612</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3661,24 +3691,14 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3730,10 +3750,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128520722</v>
+        <v>128524030</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3775,10 +3795,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488547</v>
+        <v>488370</v>
       </c>
       <c r="R26" t="n">
-        <v>7061612</v>
+        <v>7061528</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3815,7 +3835,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3829,7 +3849,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3867,38 +3887,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128524030</v>
+        <v>128522759</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>98536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3912,13 +3932,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488370</v>
+        <v>488182</v>
       </c>
       <c r="R27" t="n">
-        <v>7061528</v>
+        <v>7061439</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3952,7 +3972,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Vid en liten bäck.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3966,27 +3986,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4007,7 +4007,7 @@
         <v>128523237</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>128525134</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>128521676</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>128520359</v>
       </c>
       <c r="B31" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>128539542</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>128521198</v>
       </c>
       <c r="B33" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>128522630</v>
       </c>
       <c r="B34" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>128529638</v>
       </c>
       <c r="B35" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>128529626</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>128523788</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>128525266</v>
       </c>
       <c r="B38" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128523640</v>
       </c>
       <c r="B39" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>128524326</v>
       </c>
       <c r="B40" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>128539465</v>
       </c>
       <c r="B41" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>128529649</v>
       </c>
       <c r="B42" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128520460</v>
       </c>
       <c r="B3" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>128520214</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>128524370</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128524385</v>
       </c>
       <c r="B8" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128521099</v>
+        <v>128526315</v>
       </c>
       <c r="B9" t="n">
-        <v>91490</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,42 +1584,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Västbodarna, Västbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488553</v>
+        <v>488619</v>
       </c>
       <c r="R9" t="n">
-        <v>7061525</v>
+        <v>7061800</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1662,7 +1657,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1677,12 +1672,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1700,10 +1695,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128526315</v>
+        <v>128526246</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,13 +1730,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488619</v>
+        <v>488615</v>
       </c>
       <c r="R10" t="n">
-        <v>7061800</v>
+        <v>7061764</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1822,10 +1817,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128526246</v>
+        <v>128521099</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>91495</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,34 +1828,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västbodarna, Västbodarna, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488615</v>
+        <v>488553</v>
       </c>
       <c r="R11" t="n">
-        <v>7061764</v>
+        <v>7061525</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1947,7 +1947,7 @@
         <v>128524649</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>128522990</v>
       </c>
       <c r="B13" t="n">
-        <v>97496</v>
+        <v>97502</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2457,10 +2457,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128526042</v>
+        <v>128524584</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,42 +2468,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488537</v>
+        <v>488499</v>
       </c>
       <c r="R16" t="n">
-        <v>7061782</v>
+        <v>7061671</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2561,12 +2556,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2584,7 +2579,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128529478</v>
+        <v>128526042</v>
       </c>
       <c r="B17" t="n">
         <v>57716</v>
@@ -2613,27 +2608,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488440</v>
+        <v>488537</v>
       </c>
       <c r="R17" t="n">
-        <v>7061748</v>
+        <v>7061782</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2663,11 +2655,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2719,10 +2706,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128524584</v>
+        <v>128529478</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,37 +2717,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488499</v>
+        <v>488440</v>
       </c>
       <c r="R18" t="n">
-        <v>7061671</v>
+        <v>7061748</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2792,6 +2787,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128519986</v>
+        <v>128525407</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488586</v>
+        <v>488513</v>
       </c>
       <c r="R19" t="n">
-        <v>7061562</v>
+        <v>7061752</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2914,11 +2914,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2930,7 +2925,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2968,10 +2963,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128526001</v>
+        <v>128519986</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3003,13 +2998,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488521</v>
+        <v>488586</v>
       </c>
       <c r="R20" t="n">
-        <v>7061774</v>
+        <v>7061562</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3041,6 +3036,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3090,10 +3090,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128525407</v>
+        <v>128526001</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3125,13 +3125,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488513</v>
+        <v>488521</v>
       </c>
       <c r="R21" t="n">
-        <v>7061752</v>
+        <v>7061774</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>128520317</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>128524203</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>128522759</v>
       </c>
       <c r="B27" t="n">
-        <v>98536</v>
+        <v>98542</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128523237</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>128525134</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>128521676</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>128539542</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>128521198</v>
       </c>
       <c r="B33" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>128522630</v>
       </c>
       <c r="B34" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>128529626</v>
       </c>
       <c r="B36" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>128523788</v>
       </c>
       <c r="B37" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128523640</v>
       </c>
       <c r="B39" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>128524326</v>
       </c>
       <c r="B40" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>128539465</v>
       </c>
       <c r="B41" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128520460</v>
       </c>
       <c r="B3" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128524385</v>
       </c>
       <c r="B8" t="n">
-        <v>91495</v>
+        <v>91500</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128526315</v>
+        <v>128521099</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>91500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,37 +1584,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västbodarna, Västbodarna, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488619</v>
+        <v>488553</v>
       </c>
       <c r="R9" t="n">
-        <v>7061800</v>
+        <v>7061525</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1672,12 +1677,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1695,7 +1700,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128526246</v>
+        <v>128526315</v>
       </c>
       <c r="B10" t="n">
         <v>79120</v>
@@ -1730,13 +1735,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488615</v>
+        <v>488619</v>
       </c>
       <c r="R10" t="n">
-        <v>7061764</v>
+        <v>7061800</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1817,10 +1822,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128521099</v>
+        <v>128526246</v>
       </c>
       <c r="B11" t="n">
-        <v>91495</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,39 +1833,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Västbodarna, Västbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488553</v>
+        <v>488615</v>
       </c>
       <c r="R11" t="n">
-        <v>7061525</v>
+        <v>7061764</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
         <v>128522990</v>
       </c>
       <c r="B13" t="n">
-        <v>97502</v>
+        <v>97509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2457,10 +2457,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128524584</v>
+        <v>128529478</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,37 +2468,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488499</v>
+        <v>488440</v>
       </c>
       <c r="R16" t="n">
-        <v>7061671</v>
+        <v>7061748</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2530,6 +2538,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2556,12 +2569,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2706,10 +2719,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128529478</v>
+        <v>128524584</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2717,45 +2730,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488440</v>
+        <v>488499</v>
       </c>
       <c r="R18" t="n">
-        <v>7061748</v>
+        <v>7061671</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2787,11 +2792,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128525407</v>
+        <v>128519986</v>
       </c>
       <c r="B19" t="n">
         <v>79120</v>
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488513</v>
+        <v>488586</v>
       </c>
       <c r="R19" t="n">
-        <v>7061752</v>
+        <v>7061562</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2914,6 +2914,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2925,7 +2930,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2963,7 +2968,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128519986</v>
+        <v>128526001</v>
       </c>
       <c r="B20" t="n">
         <v>79120</v>
@@ -2998,13 +3003,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488586</v>
+        <v>488521</v>
       </c>
       <c r="R20" t="n">
-        <v>7061562</v>
+        <v>7061774</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3036,11 +3041,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3090,7 +3090,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128526001</v>
+        <v>128525407</v>
       </c>
       <c r="B21" t="n">
         <v>79120</v>
@@ -3125,13 +3125,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488521</v>
+        <v>488513</v>
       </c>
       <c r="R21" t="n">
-        <v>7061774</v>
+        <v>7061752</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128520722</v>
+        <v>128524030</v>
       </c>
       <c r="B25" t="n">
         <v>57716</v>
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488547</v>
+        <v>488370</v>
       </c>
       <c r="R25" t="n">
-        <v>7061612</v>
+        <v>7061528</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3750,7 +3750,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128524030</v>
+        <v>128520722</v>
       </c>
       <c r="B26" t="n">
         <v>57716</v>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488370</v>
+        <v>488547</v>
       </c>
       <c r="R26" t="n">
-        <v>7061528</v>
+        <v>7061612</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3890,7 +3890,7 @@
         <v>128522759</v>
       </c>
       <c r="B27" t="n">
-        <v>98542</v>
+        <v>98549</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>128521198</v>
       </c>
       <c r="B33" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>128522630</v>
       </c>
       <c r="B34" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128523640</v>
       </c>
       <c r="B39" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>128524326</v>
       </c>
       <c r="B40" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -2457,10 +2457,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128529478</v>
+        <v>128524584</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,45 +2468,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488440</v>
+        <v>488499</v>
       </c>
       <c r="R16" t="n">
-        <v>7061748</v>
+        <v>7061671</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2538,11 +2530,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2569,12 +2556,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2719,10 +2706,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128524584</v>
+        <v>128529478</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,37 +2717,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488499</v>
+        <v>488440</v>
       </c>
       <c r="R18" t="n">
-        <v>7061671</v>
+        <v>7061748</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2792,6 +2787,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128524030</v>
+        <v>128520722</v>
       </c>
       <c r="B25" t="n">
         <v>57716</v>
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488370</v>
+        <v>488547</v>
       </c>
       <c r="R25" t="n">
-        <v>7061528</v>
+        <v>7061612</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3750,7 +3750,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128520722</v>
+        <v>128524030</v>
       </c>
       <c r="B26" t="n">
         <v>57716</v>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488547</v>
+        <v>488370</v>
       </c>
       <c r="R26" t="n">
-        <v>7061612</v>
+        <v>7061528</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128524370</v>
+        <v>128520624</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,37 +1091,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488532</v>
+        <v>488560</v>
       </c>
       <c r="R5" t="n">
-        <v>7061632</v>
+        <v>7061623</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1153,6 +1158,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gammal gran  som står nära en grov asp.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1161,6 +1171,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1177,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128520624</v>
+        <v>128524370</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,42 +1223,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488560</v>
+        <v>488532</v>
       </c>
       <c r="R6" t="n">
-        <v>7061623</v>
+        <v>7061632</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,11 +1285,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gammal gran  som står nära en grov asp.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1268,31 +1293,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1573,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128521099</v>
+        <v>128526315</v>
       </c>
       <c r="B9" t="n">
-        <v>91500</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,42 +1584,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Västbodarna, Västbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488553</v>
+        <v>488619</v>
       </c>
       <c r="R9" t="n">
-        <v>7061525</v>
+        <v>7061800</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1662,7 +1657,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1677,12 +1672,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1700,7 +1695,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128526315</v>
+        <v>128526246</v>
       </c>
       <c r="B10" t="n">
         <v>79120</v>
@@ -1735,13 +1730,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488619</v>
+        <v>488615</v>
       </c>
       <c r="R10" t="n">
-        <v>7061800</v>
+        <v>7061764</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1822,7 +1817,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128526246</v>
+        <v>128524649</v>
       </c>
       <c r="B11" t="n">
         <v>79120</v>
@@ -1853,17 +1848,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västbodarna, Västbodarna, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488615</v>
+        <v>488534</v>
       </c>
       <c r="R11" t="n">
-        <v>7061764</v>
+        <v>7061682</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1890,9 +1885,19 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1944,10 +1949,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128524649</v>
+        <v>128521099</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>91500</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,37 +1960,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488534</v>
+        <v>488553</v>
       </c>
       <c r="R12" t="n">
-        <v>7061682</v>
+        <v>7061525</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2012,21 +2022,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128523976</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>128520460</v>
       </c>
       <c r="B3" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>128520214</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128520624</v>
+        <v>128524370</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,42 +1091,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488560</v>
+        <v>488532</v>
       </c>
       <c r="R5" t="n">
-        <v>7061623</v>
+        <v>7061632</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1158,11 +1153,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gammal gran  som står nära en grov asp.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1171,31 +1161,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1212,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128524370</v>
+        <v>128520624</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,37 +1188,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488532</v>
+        <v>488560</v>
       </c>
       <c r="R6" t="n">
-        <v>7061632</v>
+        <v>7061623</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1285,6 +1255,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gammal gran  som står nära en grov asp.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1293,6 +1268,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1312,7 +1312,7 @@
         <v>128526060</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128524385</v>
       </c>
       <c r="B8" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128526315</v>
+        <v>128521099</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,37 +1584,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västbodarna, Västbodarna, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488619</v>
+        <v>488553</v>
       </c>
       <c r="R9" t="n">
-        <v>7061800</v>
+        <v>7061525</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1672,12 +1677,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1695,10 +1700,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128526246</v>
+        <v>128526315</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,13 +1735,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488615</v>
+        <v>488619</v>
       </c>
       <c r="R10" t="n">
-        <v>7061764</v>
+        <v>7061800</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1817,10 +1822,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128524649</v>
+        <v>128526246</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,17 +1853,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Västbodarna, Västbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488534</v>
+        <v>488615</v>
       </c>
       <c r="R11" t="n">
-        <v>7061682</v>
+        <v>7061764</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1885,19 +1890,9 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1949,10 +1944,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128521099</v>
+        <v>128524649</v>
       </c>
       <c r="B12" t="n">
-        <v>91500</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,42 +1955,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488553</v>
+        <v>488534</v>
       </c>
       <c r="R12" t="n">
-        <v>7061525</v>
+        <v>7061682</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2022,11 +2012,21 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
         <v>128522990</v>
       </c>
       <c r="B13" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>128520994</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128520836</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>128524584</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>128526042</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128529478</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128519986</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>128526001</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>128525407</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>128520317</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>128524203</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128525531</v>
       </c>
       <c r="B24" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>128520722</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>128524030</v>
       </c>
       <c r="B26" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>128522759</v>
       </c>
       <c r="B27" t="n">
-        <v>98549</v>
+        <v>98553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128523237</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>128525134</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>128521676</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>128520359</v>
       </c>
       <c r="B31" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>128539542</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>128521198</v>
       </c>
       <c r="B33" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>128522630</v>
       </c>
       <c r="B34" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>128529638</v>
       </c>
       <c r="B35" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>128529626</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>128523788</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>128525266</v>
       </c>
       <c r="B38" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128523640</v>
       </c>
       <c r="B39" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>128524326</v>
       </c>
       <c r="B40" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>128539465</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>128529649</v>
       </c>
       <c r="B42" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -2457,10 +2457,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128524584</v>
+        <v>128526042</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,37 +2468,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488499</v>
+        <v>488537</v>
       </c>
       <c r="R16" t="n">
-        <v>7061671</v>
+        <v>7061782</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2556,12 +2561,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2579,7 +2584,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128526042</v>
+        <v>128529478</v>
       </c>
       <c r="B17" t="n">
         <v>57720</v>
@@ -2608,24 +2613,27 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488537</v>
+        <v>488440</v>
       </c>
       <c r="R17" t="n">
-        <v>7061782</v>
+        <v>7061748</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2655,6 +2663,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2706,10 +2719,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128529478</v>
+        <v>128524584</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2717,45 +2730,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488440</v>
+        <v>488499</v>
       </c>
       <c r="R18" t="n">
-        <v>7061748</v>
+        <v>7061671</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2787,11 +2792,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -2457,10 +2457,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128526042</v>
+        <v>128524584</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,42 +2468,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488537</v>
+        <v>488499</v>
       </c>
       <c r="R16" t="n">
-        <v>7061782</v>
+        <v>7061671</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2561,12 +2556,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2719,10 +2714,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128524584</v>
+        <v>128526042</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,37 +2725,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488499</v>
+        <v>488537</v>
       </c>
       <c r="R18" t="n">
-        <v>7061671</v>
+        <v>7061782</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128519986</v>
+        <v>128525407</v>
       </c>
       <c r="B19" t="n">
         <v>79124</v>
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488586</v>
+        <v>488513</v>
       </c>
       <c r="R19" t="n">
-        <v>7061562</v>
+        <v>7061752</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2914,11 +2914,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2930,7 +2925,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3090,7 +3085,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128525407</v>
+        <v>128519986</v>
       </c>
       <c r="B21" t="n">
         <v>79124</v>
@@ -3125,13 +3120,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488513</v>
+        <v>488586</v>
       </c>
       <c r="R21" t="n">
-        <v>7061752</v>
+        <v>7061562</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3163,6 +3158,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3613,7 +3613,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128520722</v>
+        <v>128524030</v>
       </c>
       <c r="B25" t="n">
         <v>57720</v>
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488547</v>
+        <v>488370</v>
       </c>
       <c r="R25" t="n">
-        <v>7061612</v>
+        <v>7061528</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3750,7 +3750,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128524030</v>
+        <v>128520722</v>
       </c>
       <c r="B26" t="n">
         <v>57720</v>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488370</v>
+        <v>488547</v>
       </c>
       <c r="R26" t="n">
-        <v>7061528</v>
+        <v>7061612</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128523976</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>128520460</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>128520214</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>128524370</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>128520624</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>128526060</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128524385</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>128521099</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>128526315</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>128526246</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>128524649</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>128522990</v>
       </c>
       <c r="B13" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>128520994</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128520836</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>128524584</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128529478</v>
+        <v>128526042</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,27 +2608,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488440</v>
+        <v>488537</v>
       </c>
       <c r="R17" t="n">
-        <v>7061748</v>
+        <v>7061782</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2658,11 +2655,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2714,10 +2706,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128526042</v>
+        <v>128529478</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2743,24 +2735,27 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488537</v>
+        <v>488440</v>
       </c>
       <c r="R18" t="n">
-        <v>7061782</v>
+        <v>7061748</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2790,6 +2785,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2841,10 +2841,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128525407</v>
+        <v>128519986</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488513</v>
+        <v>488586</v>
       </c>
       <c r="R19" t="n">
-        <v>7061752</v>
+        <v>7061562</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2914,6 +2914,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2925,7 +2930,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2966,7 +2971,7 @@
         <v>128526001</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3085,10 +3090,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128519986</v>
+        <v>128525407</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3120,13 +3125,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488586</v>
+        <v>488513</v>
       </c>
       <c r="R21" t="n">
-        <v>7061562</v>
+        <v>7061752</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3158,11 +3163,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3215,7 +3215,7 @@
         <v>128520317</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>128524203</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128525531</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128524030</v>
+        <v>128520722</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488370</v>
+        <v>488547</v>
       </c>
       <c r="R25" t="n">
-        <v>7061528</v>
+        <v>7061612</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3750,10 +3750,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128520722</v>
+        <v>128524030</v>
       </c>
       <c r="B26" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488547</v>
+        <v>488370</v>
       </c>
       <c r="R26" t="n">
-        <v>7061612</v>
+        <v>7061528</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3890,7 +3890,7 @@
         <v>128522759</v>
       </c>
       <c r="B27" t="n">
-        <v>98553</v>
+        <v>98560</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128523237</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>128525134</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>128521676</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>128520359</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>128539542</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>128521198</v>
       </c>
       <c r="B33" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>128522630</v>
       </c>
       <c r="B34" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>128529638</v>
       </c>
       <c r="B35" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>128529626</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>128523788</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>128525266</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128523640</v>
       </c>
       <c r="B39" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>128524326</v>
       </c>
       <c r="B40" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>128539465</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>128529649</v>
       </c>
       <c r="B42" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>128520460</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>128520214</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128524370</v>
+        <v>128520624</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,37 +1091,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488532</v>
+        <v>488560</v>
       </c>
       <c r="R5" t="n">
-        <v>7061632</v>
+        <v>7061623</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1153,6 +1158,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gammal gran  som står nära en grov asp.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1161,6 +1171,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1177,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128520624</v>
+        <v>128524370</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,42 +1223,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488560</v>
+        <v>488532</v>
       </c>
       <c r="R6" t="n">
-        <v>7061623</v>
+        <v>7061632</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,11 +1285,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gammal gran  som står nära en grov asp.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1268,31 +1293,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1449,7 +1449,7 @@
         <v>128524385</v>
       </c>
       <c r="B8" t="n">
-        <v>91511</v>
+        <v>91516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128526315</v>
+        <v>128521099</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>91516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,37 +1584,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västbodarna, Västbodarna, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488619</v>
+        <v>488553</v>
       </c>
       <c r="R9" t="n">
-        <v>7061800</v>
+        <v>7061525</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1672,12 +1677,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1695,10 +1700,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128526246</v>
+        <v>128526315</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,13 +1735,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488615</v>
+        <v>488619</v>
       </c>
       <c r="R10" t="n">
-        <v>7061764</v>
+        <v>7061800</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1817,10 +1822,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128524649</v>
+        <v>128526246</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,17 +1853,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Västbodarna, Västbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488534</v>
+        <v>488615</v>
       </c>
       <c r="R11" t="n">
-        <v>7061682</v>
+        <v>7061764</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1885,19 +1890,9 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1949,10 +1944,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128521099</v>
+        <v>128524649</v>
       </c>
       <c r="B12" t="n">
-        <v>91511</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,42 +1955,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488553</v>
+        <v>488534</v>
       </c>
       <c r="R12" t="n">
-        <v>7061525</v>
+        <v>7061682</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2022,11 +2012,21 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
         <v>128522990</v>
       </c>
       <c r="B13" t="n">
-        <v>97523</v>
+        <v>97528</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>128524584</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128519986</v>
+        <v>128526001</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488586</v>
+        <v>488521</v>
       </c>
       <c r="R19" t="n">
-        <v>7061562</v>
+        <v>7061774</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2914,11 +2914,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2930,7 +2925,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2968,10 +2963,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128526001</v>
+        <v>128525407</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3003,13 +2998,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488521</v>
+        <v>488513</v>
       </c>
       <c r="R20" t="n">
-        <v>7061774</v>
+        <v>7061752</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3090,10 +3085,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128525407</v>
+        <v>128519986</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3125,13 +3120,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488513</v>
+        <v>488586</v>
       </c>
       <c r="R21" t="n">
-        <v>7061752</v>
+        <v>7061562</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3163,6 +3158,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3215,7 +3215,7 @@
         <v>128520317</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>128524203</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3466,38 +3466,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128522759</v>
+        <v>128525531</v>
       </c>
       <c r="B24" t="n">
-        <v>98563</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488182</v>
+        <v>488486</v>
       </c>
       <c r="R24" t="n">
-        <v>7061439</v>
+        <v>7061727</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3544,14 +3544,24 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Vid en liten bäck.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3566,6 +3576,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3583,7 +3613,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128525531</v>
+        <v>128520722</v>
       </c>
       <c r="B25" t="n">
         <v>57723</v>
@@ -3628,13 +3658,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488486</v>
+        <v>488547</v>
       </c>
       <c r="R25" t="n">
-        <v>7061727</v>
+        <v>7061612</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3661,24 +3691,14 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3730,7 +3750,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128520722</v>
+        <v>128524030</v>
       </c>
       <c r="B26" t="n">
         <v>57723</v>
@@ -3775,10 +3795,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488547</v>
+        <v>488370</v>
       </c>
       <c r="R26" t="n">
-        <v>7061612</v>
+        <v>7061528</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3815,7 +3835,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3829,7 +3849,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3867,38 +3887,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128524030</v>
+        <v>128522759</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>98568</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3912,13 +3932,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488370</v>
+        <v>488182</v>
       </c>
       <c r="R27" t="n">
-        <v>7061528</v>
+        <v>7061439</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3952,7 +3972,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Vid en liten bäck.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3966,27 +3986,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4007,7 +4007,7 @@
         <v>128523237</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>128525134</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>128521676</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>128539542</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>128521198</v>
       </c>
       <c r="B33" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>128522630</v>
       </c>
       <c r="B34" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>128529626</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>128523788</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128523640</v>
       </c>
       <c r="B39" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>128524326</v>
       </c>
       <c r="B40" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>128539465</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -2841,7 +2841,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128526001</v>
+        <v>128519986</v>
       </c>
       <c r="B19" t="n">
         <v>79034</v>
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488521</v>
+        <v>488586</v>
       </c>
       <c r="R19" t="n">
-        <v>7061774</v>
+        <v>7061562</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2914,6 +2914,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2925,7 +2930,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2963,7 +2968,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128525407</v>
+        <v>128526001</v>
       </c>
       <c r="B20" t="n">
         <v>79034</v>
@@ -2998,13 +3003,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488513</v>
+        <v>488521</v>
       </c>
       <c r="R20" t="n">
-        <v>7061752</v>
+        <v>7061774</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3085,7 +3090,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128519986</v>
+        <v>128525407</v>
       </c>
       <c r="B21" t="n">
         <v>79034</v>
@@ -3120,13 +3125,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488586</v>
+        <v>488513</v>
       </c>
       <c r="R21" t="n">
-        <v>7061562</v>
+        <v>7061752</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3158,11 +3163,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3466,38 +3466,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128525531</v>
+        <v>128522759</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>98568</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488486</v>
+        <v>488182</v>
       </c>
       <c r="R24" t="n">
-        <v>7061727</v>
+        <v>7061439</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3544,24 +3544,14 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Vid en liten bäck.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3576,26 +3566,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3613,7 +3583,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128520722</v>
+        <v>128525531</v>
       </c>
       <c r="B25" t="n">
         <v>57723</v>
@@ -3658,13 +3628,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488547</v>
+        <v>488486</v>
       </c>
       <c r="R25" t="n">
-        <v>7061612</v>
+        <v>7061727</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3691,14 +3661,24 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3750,7 +3730,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128524030</v>
+        <v>128520722</v>
       </c>
       <c r="B26" t="n">
         <v>57723</v>
@@ -3795,10 +3775,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488370</v>
+        <v>488547</v>
       </c>
       <c r="R26" t="n">
-        <v>7061528</v>
+        <v>7061612</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3835,7 +3815,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3849,7 +3829,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3887,38 +3867,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128522759</v>
+        <v>128524030</v>
       </c>
       <c r="B27" t="n">
-        <v>98568</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3932,13 +3912,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488182</v>
+        <v>488370</v>
       </c>
       <c r="R27" t="n">
-        <v>7061439</v>
+        <v>7061528</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3972,7 +3952,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Vid en liten bäck.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3986,7 +3966,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -4525,7 +4525,7 @@
         <v>128539542</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>128521198</v>
       </c>
       <c r="B33" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>128522630</v>
       </c>
       <c r="B34" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>128529626</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>128523788</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>128523640</v>
       </c>
       <c r="B39" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>128524326</v>
       </c>
       <c r="B40" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>128539465</v>
       </c>
       <c r="B41" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128523976</v>
+        <v>128521099</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,32 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488369</v>
+        <v>488553</v>
       </c>
       <c r="R2" t="n">
-        <v>7061519</v>
+        <v>7061525</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre (&lt;10 år gamla), på stambasen av en gran. Minst medelhögt livsmiljövärde för tretåig hackspett baserat på stående död ved på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128520460</v>
+        <v>128524385</v>
       </c>
       <c r="B3" t="n">
-        <v>91538</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,33 +813,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -861,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488600</v>
+        <v>488540</v>
       </c>
       <c r="R3" t="n">
-        <v>7061613</v>
+        <v>7061624</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,11 +880,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer i en stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -915,7 +891,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -930,12 +906,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -953,14 +929,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128520214</v>
+        <v>128519986</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -988,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488605</v>
+        <v>488586</v>
       </c>
       <c r="R4" t="n">
-        <v>7061603</v>
+        <v>7061562</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1028,7 +1004,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,50 +1056,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128520624</v>
+        <v>128520214</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488560</v>
+        <v>488605</v>
       </c>
       <c r="R5" t="n">
-        <v>7061623</v>
+        <v>7061603</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1160,7 +1131,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal gran  som står nära en grov asp.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,12 +1160,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1212,14 +1183,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128524370</v>
+        <v>128520317</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1247,13 +1218,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488532</v>
+        <v>488655</v>
       </c>
       <c r="R6" t="n">
-        <v>7061632</v>
+        <v>7061610</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1285,6 +1256,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer här rikligt på en gran.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1293,6 +1269,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1309,53 +1310,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128526060</v>
+        <v>128521676</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488550</v>
+        <v>488404</v>
       </c>
       <c r="R7" t="n">
-        <v>7061788</v>
+        <v>7061490</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1382,19 +1378,14 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>19:02</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>19:02</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,7 +1399,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1423,12 +1414,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1446,50 +1437,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128524385</v>
+        <v>128523055</v>
       </c>
       <c r="B8" t="n">
-        <v>91516</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488540</v>
+        <v>488245</v>
       </c>
       <c r="R8" t="n">
-        <v>7061624</v>
+        <v>7061460</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1550,12 +1536,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1573,53 +1559,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128521099</v>
+        <v>128523237</v>
       </c>
       <c r="B9" t="n">
-        <v>91516</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488553</v>
+        <v>488340</v>
       </c>
       <c r="R9" t="n">
-        <v>7061525</v>
+        <v>7061501</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1677,12 +1658,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1700,14 +1681,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128526315</v>
+        <v>128523788</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1731,17 +1712,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västbodarna, Västbodarna, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488619</v>
+        <v>488308</v>
       </c>
       <c r="R10" t="n">
-        <v>7061800</v>
+        <v>7061548</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1771,6 +1752,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1822,14 +1808,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128526246</v>
+        <v>128524203</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1853,14 +1839,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västbodarna, Västbodarna, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488615</v>
+        <v>488385</v>
       </c>
       <c r="R11" t="n">
-        <v>7061764</v>
+        <v>7061494</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1895,6 +1881,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1906,7 +1897,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1944,14 +1935,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128524649</v>
+        <v>128524370</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1979,13 +1970,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488534</v>
+        <v>488532</v>
       </c>
       <c r="R12" t="n">
-        <v>7061682</v>
+        <v>7061632</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2012,21 +2003,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2035,31 +2016,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2076,53 +2032,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128522990</v>
+        <v>128524584</v>
       </c>
       <c r="B13" t="n">
-        <v>97528</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488248</v>
+        <v>488499</v>
       </c>
       <c r="R13" t="n">
-        <v>7061430</v>
+        <v>7061671</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2166,6 +2117,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2183,58 +2154,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128520994</v>
+        <v>128524649</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488540</v>
+        <v>488534</v>
       </c>
       <c r="R14" t="n">
-        <v>7061556</v>
+        <v>7061682</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2261,14 +2222,19 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2282,7 +2248,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2297,12 +2263,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2320,58 +2286,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128520836</v>
+        <v>128525134</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488552</v>
+        <v>488563</v>
       </c>
       <c r="R15" t="n">
-        <v>7061599</v>
+        <v>7061757</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2398,14 +2354,19 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död gran med full längd (26 cm i brösthöjdsdiameter) där det också finns födosökspår efter hackspett. Fyndplatsen finns i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2419,7 +2380,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2434,12 +2395,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2457,14 +2418,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128524584</v>
+        <v>128525407</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2492,13 +2453,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488499</v>
+        <v>488513</v>
       </c>
       <c r="R16" t="n">
-        <v>7061671</v>
+        <v>7061752</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2579,53 +2540,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128526042</v>
+        <v>128526001</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488537</v>
+        <v>488521</v>
       </c>
       <c r="R17" t="n">
-        <v>7061782</v>
+        <v>7061774</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2683,12 +2639,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2706,56 +2662,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128529478</v>
+        <v>128526246</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+          <t>Västbodarna, Västbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488440</v>
+        <v>488615</v>
       </c>
       <c r="R18" t="n">
-        <v>7061748</v>
+        <v>7061764</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2787,11 +2735,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2818,12 +2761,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2841,14 +2784,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128519986</v>
+        <v>128526315</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2872,17 +2815,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Västbodarna, Västbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488586</v>
+        <v>488619</v>
       </c>
       <c r="R19" t="n">
-        <v>7061562</v>
+        <v>7061800</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2914,11 +2857,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2930,7 +2868,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2968,14 +2906,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128526001</v>
+        <v>128529626</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2997,16 +2935,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488521</v>
+        <v>488560</v>
       </c>
       <c r="R20" t="n">
-        <v>7061774</v>
+        <v>7061522</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3041,18 +2982,24 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3090,14 +3037,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128525407</v>
+        <v>128539465</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3119,19 +3066,22 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488513</v>
+        <v>488595</v>
       </c>
       <c r="R21" t="n">
-        <v>7061752</v>
+        <v>7061669</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3163,18 +3113,24 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3189,12 +3145,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3212,14 +3168,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128520317</v>
+        <v>128539542</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3241,19 +3197,22 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488655</v>
+        <v>488565</v>
       </c>
       <c r="R22" t="n">
-        <v>7061610</v>
+        <v>7061714</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3285,23 +3244,19 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växer här rikligt på en gran.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3316,12 +3271,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3339,10 +3294,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128524203</v>
+        <v>128519879</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3350,37 +3305,49 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488385</v>
+        <v>488633</v>
       </c>
       <c r="R23" t="n">
-        <v>7061494</v>
+        <v>7061544</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3414,7 +3381,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, äldre, i riklig mängd längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3428,7 +3395,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3443,12 +3410,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3466,38 +3433,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128522759</v>
+        <v>128520359</v>
       </c>
       <c r="B24" t="n">
-        <v>98568</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3511,10 +3478,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488182</v>
+        <v>488614</v>
       </c>
       <c r="R24" t="n">
-        <v>7061439</v>
+        <v>7061641</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3551,7 +3518,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Vid en liten bäck.</t>
+          <t>Ringhack, äldre, tydligt på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3565,7 +3532,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3583,10 +3570,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128525531</v>
+        <v>128520624</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3617,24 +3604,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488486</v>
+        <v>488560</v>
       </c>
       <c r="R25" t="n">
-        <v>7061727</v>
+        <v>7061623</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3661,24 +3643,14 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal gran  som står nära en grov asp.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3692,7 +3664,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3733,7 +3705,7 @@
         <v>128520722</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3867,10 +3839,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128524030</v>
+        <v>128520836</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3912,13 +3884,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488370</v>
+        <v>488552</v>
       </c>
       <c r="R27" t="n">
-        <v>7061528</v>
+        <v>7061599</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3952,7 +3924,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en stående död gran med full längd (26 cm i brösthöjdsdiameter) där det också finns födosökspår efter hackspett. Fyndplatsen finns i gammal flerskiktad barrblandskog med bitvis medelhögt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3981,12 +3953,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4004,10 +3976,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128523237</v>
+        <v>128520994</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4015,37 +3987,47 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488340</v>
+        <v>488540</v>
       </c>
       <c r="R28" t="n">
-        <v>7061501</v>
+        <v>7061556</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4077,6 +4059,11 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4103,12 +4090,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4126,10 +4113,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128525134</v>
+        <v>128521346</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4137,34 +4124,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488563</v>
+        <v>488515</v>
       </c>
       <c r="R29" t="n">
-        <v>7061757</v>
+        <v>7061501</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
@@ -4194,19 +4191,14 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>18:22</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>18:22</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4220,7 +4212,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4235,12 +4227,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4258,10 +4250,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128521676</v>
+        <v>128521444</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4269,34 +4261,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488404</v>
+        <v>488479</v>
       </c>
       <c r="R30" t="n">
-        <v>7061490</v>
+        <v>7061484</v>
       </c>
       <c r="S30" t="n">
         <v>8</v>
@@ -4333,7 +4335,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4362,12 +4364,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4385,10 +4387,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128520359</v>
+        <v>128521582</v>
       </c>
       <c r="B31" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4430,13 +4432,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488614</v>
+        <v>488464</v>
       </c>
       <c r="R31" t="n">
-        <v>7061641</v>
+        <v>7061484</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4470,7 +4472,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, tydligt på stambasen av en gran.</t>
+          <t>Ringhack, äldre, högt upp på stammen av en gran vid hyggeskanten. Fyndplatsen finns i gammal flerskiktad granskog med bitvis minst medelhögt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4522,10 +4524,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128539542</v>
+        <v>128523976</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4533,40 +4535,47 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488565</v>
+        <v>488369</v>
       </c>
       <c r="R32" t="n">
-        <v>7061714</v>
+        <v>7061519</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4598,19 +4607,23 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre (&lt;10 år gamla), på stambasen av en gran. Minst medelhögt livsmiljövärde för tretåig hackspett baserat på stående död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4625,12 +4638,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4648,50 +4661,40 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128521198</v>
+        <v>128524030</v>
       </c>
       <c r="B33" t="n">
-        <v>98659</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4703,13 +4706,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488531</v>
+        <v>488370</v>
       </c>
       <c r="R33" t="n">
-        <v>7061541</v>
+        <v>7061528</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4743,7 +4746,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 77 plantor, 7 överblommade blomställningar och 3  vinterståndare (som släppt sina frön) inom ca 3 m2 yta i gammal flerskiktad granskog.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4752,13 +4755,32 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4776,47 +4798,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128522630</v>
+        <v>128525266</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4830,13 +4843,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488211</v>
+        <v>488561</v>
       </c>
       <c r="R34" t="n">
-        <v>7061410</v>
+        <v>7061766</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4870,7 +4883,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 130 plantor, 5 överblommade blomställningar och 3 avfröade vinterståndare inom ca 1 m2 yta nära ett igensatt dike.</t>
+          <t>Ringhack, färska och äldre, på en något smalare gran. I skogsbeståndet där fyndplatsen ligger  finns partier med medelhögt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4885,6 +4898,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4902,10 +4935,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128529638</v>
+        <v>128525531</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4931,27 +4964,29 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488589</v>
+        <v>488486</v>
       </c>
       <c r="R35" t="n">
-        <v>7061562</v>
+        <v>7061727</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4978,11 +5013,21 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
           <t>Ringhack, äldre, på stambasen.</t>
@@ -4999,7 +5044,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5037,10 +5082,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128529626</v>
+        <v>128526042</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5048,40 +5093,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488560</v>
+        <v>488537</v>
       </c>
       <c r="R36" t="n">
-        <v>7061522</v>
+        <v>7061782</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5113,24 +5160,18 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5145,12 +5186,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5168,10 +5209,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128523788</v>
+        <v>128526060</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5179,37 +5220,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488308</v>
+        <v>488550</v>
       </c>
       <c r="R37" t="n">
-        <v>7061548</v>
+        <v>7061788</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5236,14 +5282,19 @@
           <t>2025-09-18</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5272,12 +5323,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5295,10 +5346,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128525266</v>
+        <v>128529478</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5324,29 +5375,27 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488561</v>
+        <v>488440</v>
       </c>
       <c r="R38" t="n">
-        <v>7061766</v>
+        <v>7061748</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5380,7 +5429,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en något smalare gran. I skogsbeståndet där fyndplatsen ligger  finns partier med medelhögt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack, äldre. Tydligt och i riklig mängd på en gammal gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5432,67 +5481,56 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128523640</v>
+        <v>128529505</v>
       </c>
       <c r="B39" t="n">
-        <v>98659</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488340</v>
+        <v>488641</v>
       </c>
       <c r="R39" t="n">
-        <v>7061493</v>
+        <v>7061537</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5526,7 +5564,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minst 400 plantor och 21 överblommade blomställningar inom ca 8 m2 yta i gammal flerskiktad granskog.</t>
+          <t>Ringhack, äldre, en bra bit upp på stammen av en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5540,7 +5578,27 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5558,67 +5616,56 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128524326</v>
+        <v>128529548</v>
       </c>
       <c r="B40" t="n">
-        <v>98659</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488460</v>
+        <v>488630</v>
       </c>
       <c r="R40" t="n">
-        <v>7061510</v>
+        <v>7061533</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5652,7 +5699,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 1 överblommad blomställning inom ca 2 x 1 m2 yta.</t>
+          <t>Ringhack, äldre, långt upp på en granstam vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5666,7 +5713,27 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5684,10 +5751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128539465</v>
+        <v>128529559</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5695,40 +5762,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488595</v>
+        <v>488621</v>
       </c>
       <c r="R41" t="n">
-        <v>7061669</v>
+        <v>7061531</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5762,7 +5830,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, några meter upp på en granstam vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5771,13 +5839,12 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5792,12 +5859,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5815,10 +5882,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128529649</v>
+        <v>128529590</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5858,13 +5925,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488607</v>
+        <v>488612</v>
       </c>
       <c r="R42" t="n">
-        <v>7061620</v>
+        <v>7061530</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5898,7 +5965,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en knäckt död gran.</t>
+          <t>Ringhack, äldre, några meter upp på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5912,7 +5979,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -5927,12 +5994,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5947,6 +6014,1538 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128529617</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>488600</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7061525</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack med tydliga kådaflöden på en gran nära hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128529635</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>488533</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7061500</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, enstaka färska bland rikligt med äldre längs flera meter på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128529638</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>488589</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7061562</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128529649</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>488607</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7061620</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en knäckt död gran.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128529668</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>488499</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7061488</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack längs några meter på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128538855</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Forsåsen, Föllinge, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>488521</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7061496</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128522759</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>488182</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7061439</v>
+      </c>
+      <c r="S49" t="n">
+        <v>9</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Vid en liten bäck.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128521198</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>488531</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7061541</v>
+      </c>
+      <c r="S50" t="n">
+        <v>9</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Minst 77 plantor, 7 överblommade blomställningar och 3  vinterståndare (som släppt sina frön) inom ca 3 m2 yta i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128522630</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>488211</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7061410</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 130 plantor, 5 överblommade blomställningar och 3 avfröade vinterståndare inom ca 1 m2 yta nära ett igensatt dike.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128523640</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>488340</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7061493</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Minst 400 plantor och 21 överblommade blomställningar inom ca 8 m2 yta i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128524326</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>488460</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7061510</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Minst 80 plantor och 1 överblommad blomställning inom ca 2 x 1 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128522990</v>
+      </c>
+      <c r="B54" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>488248</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7061430</v>
+      </c>
+      <c r="S54" t="n">
+        <v>8</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37408-2025 artfynd.xlsx
+++ b/artfynd/A 37408-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128521099</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128524385</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1053,6 +1068,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519986</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1180,6 +1200,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128520214</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1307,6 +1332,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128520317</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1434,6 +1464,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128521676</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1556,6 +1591,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128523055</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1678,6 +1718,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128523237</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1805,6 +1850,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128523788</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1932,6 +1982,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128524203</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2029,6 +2084,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128524370</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2151,6 +2211,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128524584</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2283,6 +2348,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128524649</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2415,6 +2485,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128525134</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2537,6 +2612,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128525407</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2659,6 +2739,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526001</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2781,6 +2866,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526246</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2903,6 +2993,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526315</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3034,6 +3129,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128529626</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3165,6 +3265,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128539465</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3291,6 +3396,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128539542</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3430,6 +3540,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519879</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3567,6 +3682,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128520359</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3699,6 +3819,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128520624</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3836,6 +3961,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128520722</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3973,6 +4103,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128520836</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4110,6 +4245,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128520994</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4247,6 +4387,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128521346</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4384,6 +4529,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128521444</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4521,6 +4671,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128521582</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4658,6 +4813,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128523976</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4795,6 +4955,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128524030</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4932,6 +5097,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128525266</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5079,6 +5249,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128525531</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5206,6 +5381,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526042</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5343,6 +5523,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526060</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5478,6 +5663,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128529478</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5613,6 +5803,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128529505</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5748,6 +5943,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128529548</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5879,6 +6079,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128529559</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6014,6 +6219,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128529590</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6145,6 +6355,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128529617</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6280,6 +6495,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128529635</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6415,6 +6635,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128529638</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6550,6 +6775,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128529649</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6681,6 +6911,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128529668</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6816,6 +7051,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128538855</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6933,6 +7173,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128522759</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7061,6 +7306,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128521198</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7187,6 +7437,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128522630</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7313,6 +7568,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128523640</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7439,6 +7699,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128524326</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7546,8 +7811,68 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128522990</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>